--- a/analytics_aptechka.xlsx
+++ b/analytics_aptechka.xlsx
@@ -57,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B4E00"/>
+        <fgColor rgb="00EFF3FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFF3FB"/>
+        <fgColor rgb="008B4E00"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,14 +102,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -536,68 +536,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
+        <v>291461984</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:15</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:15</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>1273451178</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 02:26</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>19.06.2026 00:36</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>19.06.2026 00:36</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>291461984</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>19.06.2026 01:15</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -619,152 +619,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Этап воронки</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Кол-во пользователей</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>% от старта</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>🚀 Зашёл в бот</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>📝 Ввёл имя</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>📝 Ввёл имя</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>👶 Выбрал сегмент</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>👶 Выбрал сегмент</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>📄 Получил гайд</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>📄 Получил гайд</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>✅ Открыл гайд</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>✅ Открыл гайд</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>▶️ День 1 — видео</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>▶️ День 1 — видео</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>📖 День 2 — история</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>📖 День 2 — история</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>🔥 День 3 — горячий лид</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>🔥 День 3 — горячий лид</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>💌 День 4 — оффер</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>💌 День 4 — оффер</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -829,130 +829,238 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:15</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>291461984</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:15</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>291461984</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:14</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>19.06.2026 00:36</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>1273451178</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 00:36</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 02:26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>дорогая мама</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>bot_started</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>19.06.2026 00:36</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 02:26</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>1273451178</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>дорогая мама</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>webinar_offered</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>19.06.2026 01:14</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="E9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 03:33</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>1273451178</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>дорогая мама</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>bot_started</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>19.06.2026 01:14</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 03:33</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>1273451178</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>дорогая мама</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>webinar_offered</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>19.06.2026 01:15</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>291461984</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>дорогая мама</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>bot_started</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>19.06.2026 01:15</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>291461984</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>дорогая мама</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>webinar_offered</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/analytics_aptechka.xlsx
+++ b/analytics_aptechka.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 02:26</t>
+          <t>19.06.2026 09:17</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -831,11 +831,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19.06.2026 01:15</t>
+          <t>19.06.2026 10:58</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>291461984</v>
+        <v>1273451178</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 01:15</t>
+          <t>19.06.2026 09:17</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>291461984</v>
+        <v>1273451178</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19.06.2026 01:14</t>
+          <t>19.06.2026 09:17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>webinar_offered</t>
+          <t>bot_started</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 01:14</t>
+          <t>19.06.2026 03:33</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -931,7 +931,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19.06.2026 00:36</t>
+          <t>19.06.2026 03:33</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -944,7 +944,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>bot_started</t>
+          <t>webinar_offered</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 00:36</t>
+          <t>19.06.2026 02:26</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>дорогая мама</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -997,54 +997,66 @@
           <t>bot_started</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 02:26</t>
+          <t>19.06.2026 01:15</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1273451178</v>
+        <v>291461984</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>дорогая мама</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>webinar_offered</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>19.06.2026 03:33</t>
+          <t>19.06.2026 01:15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1273451178</v>
+        <v>291461984</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>дорогая мама</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>bot_started</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026 03:33</t>
+          <t>19.06.2026 01:14</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1052,15 +1064,115 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 01:14</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 00:36</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>bot_started</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026 00:36</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>webinar_offered</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>19.06.2026 10:59</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1273451178</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>дорогая мама</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>webinar_offered</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
